--- a/epm/epmresults_export.xlsx
+++ b/epm/epmresults_export.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07623250427052</v>
+        <v>76.27007573639997</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07623250427051999</v>
+        <v>76.27007573639997</v>
       </c>
     </row>
     <row r="6">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>87.51144763850183</v>
+        <v>87.51144763850185</v>
       </c>
     </row>
     <row r="7">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2119.551930092374</v>
+        <v>2062.704944369833</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1926.408302943732</v>
+        <v>2097.219833832258</v>
       </c>
     </row>
     <row r="10">
@@ -646,7 +646,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bagasse</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.09843392</v>
+        <v>0.01572681128924881</v>
       </c>
     </row>
     <row r="13">
@@ -666,7 +666,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bagasse</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -675,18 +675,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.09843392</v>
+        <v>0.0157268112892488</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Bagasse</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -695,18 +695,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32.18518439839832</v>
+        <v>1.09843392</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Bagasse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>32.18518439839831</v>
+        <v>1.09843392</v>
       </c>
     </row>
     <row r="16">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6.172376383042078</v>
+        <v>9.047272702258056</v>
       </c>
     </row>
     <row r="19">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>54.39248175947514</v>
+        <v>68.86109290547333</v>
       </c>
     </row>
     <row r="20">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>54.43087755802166</v>
+        <v>66.01089364380574</v>
       </c>
     </row>
     <row r="21">
@@ -826,7 +826,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>HFO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.95248799520001</v>
+        <v>12.64120752070446</v>
       </c>
     </row>
     <row r="22">
@@ -846,7 +846,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>HFO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -855,33 +855,33 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.9524879952</v>
+        <v>6.9798078335178</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Biomass</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3.723</v>
+        <v>12.95248799520001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -891,22 +891,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.019604508446718</v>
+        <v>12.9524879952</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>Biomass</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -915,18 +915,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.019604508446718</v>
+        <v>3.723</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -935,18 +935,18 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.47643</v>
+        <v>0.04157567272235999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -955,18 +955,18 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.932810434834116</v>
+        <v>0.04157567272236</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -975,38 +975,38 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9.706100708640005</v>
+        <v>0.417852</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HFO</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>24.0693642432</v>
+        <v>0.417852</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Biomass</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1015,18 +1015,18 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3.324639</v>
+        <v>19.64139369309</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Biomass</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.324639</v>
+        <v>19.64139369309001</v>
       </c>
     </row>
     <row r="32">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Biomass</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>87.44239979264555</v>
+        <v>2.4957564</v>
       </c>
     </row>
     <row r="33">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Biomass</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>85.35395800509015</v>
+        <v>2.4957564</v>
       </c>
     </row>
     <row r="34">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HFO</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1095,33 +1095,33 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.9365087231624644</v>
+        <v>30.66851419396262</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.07192094930433057</v>
+        <v>29.15818815108339</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1131,11 +1131,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.02053453250184594</v>
+        <v>2.896622053880954</v>
       </c>
     </row>
     <row r="37">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.755342037241998</v>
+        <v>2.963005726870068</v>
       </c>
     </row>
     <row r="38">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>HFO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4.019499719999997</v>
+        <v>0.09664908000000011</v>
       </c>
     </row>
     <row r="39">
@@ -1191,11 +1191,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.09664908000000007</v>
+        <v>0.09664908000000008</v>
       </c>
     </row>
   </sheetData>
@@ -1209,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D166"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>212842.6206413242</v>
+        <v>215421.5416</v>
       </c>
     </row>
     <row r="4">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>213278.4933396553</v>
+        <v>224688.3340000001</v>
       </c>
     </row>
     <row r="5">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14483.60141974093</v>
+        <v>215421.5416000002</v>
       </c>
     </row>
     <row r="6">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1329,18 +1329,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14899.1751219946</v>
+        <v>224688.3339999997</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Exports exchange: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1349,18 +1349,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11325.33640427556</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Exports exchange: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1369,18 +1369,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2893.36745677001</v>
+        <v>1143.000000000002</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1389,18 +1389,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3158.265015465366</v>
+        <v>548.0329239999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1409,18 +1409,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12005.80766522459</v>
+        <v>548.0329239999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Unmet demand: GWh</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1429,18 +1429,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01466085978221114</v>
+        <v>528.9670759999998</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Unmet demand: GWh</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1449,13 +1449,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05343315984186614</v>
+        <v>594.9670760000009</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>215421.5416000002</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1489,13 +1489,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>224688.3339999997</v>
+        <v>1143.000000000002</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1077</v>
+        <v>1391.629174999998</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1143.000000000002</v>
+        <v>1479.182004000004</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>612.8569240000004</v>
+        <v>424.608207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>616.7156785307833</v>
+        <v>553.596668910856</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.851289516910033</v>
+        <v>967.0209679999995</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1609,18 +1609,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7.850210658046547</v>
+        <v>925.7072817297912</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1629,18 +1629,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>469.6854964113163</v>
+        <v>1391.629174999998</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1649,18 +1649,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>533.3894039238519</v>
+        <v>1479.182004000004</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1669,18 +1669,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>469.6854964113163</v>
+        <v>7519.650270999993</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1689,18 +1689,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>533.3894039238519</v>
+        <v>8170.623188999983</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1709,18 +1709,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.4361053819975081</v>
+        <v>7519.650270999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1729,13 +1729,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.4666573962588372</v>
+        <v>8170.623188999992</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1749,13 +1749,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1077</v>
+        <v>7519.650270999993</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1143.000000000002</v>
+        <v>8170.623188999983</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1391.629174999998</v>
+        <v>11795.41443000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1479.182004000004</v>
+        <v>12800.12181999998</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>455.0684549999989</v>
+        <v>11795.41443000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1849,18 +1849,18 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>518.7768277499991</v>
+        <v>12800.12181999998</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1869,18 +1869,18 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>975.5840833333349</v>
+        <v>11795.41443000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1889,18 +1889,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1001.439559461809</v>
+        <v>12800.12181999998</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1909,18 +1909,18 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>975.5840833333349</v>
+        <v>4342.093871000006</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1929,18 +1929,18 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1001.439559461809</v>
+        <v>4717.276214000007</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1949,18 +1949,18 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.7010373890252311</v>
+        <v>2569.65648</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1969,18 +1969,18 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.6770225413463093</v>
+        <v>2541.022522000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Total Demand: GWh</t>
+          <t>Unmet demand: GWh</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1989,18 +1989,18 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1391.629174999998</v>
+        <v>1772.437391000002</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Total Demand: GWh</t>
+          <t>Unmet demand: GWh</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2009,18 +2009,18 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1479.182004000004</v>
+        <v>2178.07631644445</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Demand: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2029,18 +2029,18 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7519.650270999993</v>
+        <v>4342.093871000006</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Demand: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2049,18 +2049,18 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8170.623188999983</v>
+        <v>4717.276214000007</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Total production: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2069,18 +2069,18 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>19478.3573002876</v>
+        <v>4355.145617000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Total production: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2089,18 +2089,18 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>19720.88304361449</v>
+        <v>4485.45373400001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2109,18 +2109,18 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3346.031097793282</v>
+        <v>1715.999011528001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2129,18 +2129,18 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3441.016723332688</v>
+        <v>2656.322177528</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Exports exchange: GWh</t>
+          <t>Unmet demand: GWh</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2149,18 +2149,18 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>15170.89688316913</v>
+        <v>2639.146605472003</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Exports exchange: GWh</t>
+          <t>Unmet demand: GWh</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2169,18 +2169,18 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14850.40687429903</v>
+        <v>1829.131556472004</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2189,18 +2189,18 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-11824.86578537585</v>
+        <v>4355.145617000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2209,18 +2209,18 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-11409.39015096634</v>
+        <v>4485.45373400001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2229,18 +2229,18 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-1.572528689396526</v>
+        <v>14390.00000000004</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2249,18 +2249,18 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-1.396391668915373</v>
+        <v>15337.00000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Total Demand: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2269,18 +2269,18 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7519.650270999993</v>
+        <v>14390.00000000003</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Total Demand: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2289,18 +2289,18 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>8170.623188999983</v>
+        <v>15337.00000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Demand: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2309,18 +2309,18 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11795.41443000001</v>
+        <v>14390.00000000004</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Demand: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2329,18 +2329,18 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12800.12181999998</v>
+        <v>15337.00000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Total production: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2349,18 +2349,18 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13615.85446894751</v>
+        <v>16637.87143000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Total production: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2369,18 +2369,18 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14579.35940321673</v>
+        <v>17697.40276</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2389,18 +2389,18 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4502.64</v>
+        <v>16637.87143</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2409,18 +2409,18 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4502.64</v>
+        <v>17697.40275999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Exports exchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2429,18 +2429,18 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6142.974438947507</v>
+        <v>16637.87143000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Exports exchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2449,18 +2449,18 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6101.771983216755</v>
+        <v>17697.40276</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2469,18 +2469,18 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-1640.334438947507</v>
+        <v>12153.14516999996</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2489,18 +2489,18 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-1599.131983216755</v>
+        <v>13326.08802000002</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2509,18 +2509,18 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-0.1390654350198618</v>
+        <v>12153.14516999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2529,13 +2529,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>-0.1249309971970842</v>
+        <v>13326.08802000002</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11795.41443000001</v>
+        <v>12153.14516999996</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12800.12181999998</v>
+        <v>13326.08802000002</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2589,13 +2589,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4342.093871000006</v>
+        <v>7123.117210999982</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4717.276214000007</v>
+        <v>7704.363575</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1355.95848</v>
+        <v>7123.11721100001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2649,18 +2649,18 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2348.2216475</v>
+        <v>7704.363574999998</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2669,18 +2669,18 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4272.245275843799</v>
+        <v>7123.117210999982</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2689,18 +2689,18 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4252.367803226033</v>
+        <v>7704.363575</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Exports exchange: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2709,18 +2709,18 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>987.1613735754213</v>
+        <v>2526.620252999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Exports exchange: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2729,18 +2729,18 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1580.261801530033</v>
+        <v>2722.295029999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2749,18 +2749,18 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3285.083902268378</v>
+        <v>2456.51756879221</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Total production: GWh</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2769,18 +2769,18 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2672.106001696</v>
+        <v>2631.132981134511</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Unmet demand: GWh</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2789,18 +2789,18 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.7565667624573502</v>
+        <v>70.11428370013145</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Unmet demand: GWh</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.5664510366735961</v>
+        <v>91.75337398741404</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4342.093871000006</v>
+        <v>2526.620252999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2849,13 +2849,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4717.276214000007</v>
+        <v>2722.295029999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2869,13 +2869,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4355.145617000001</v>
+        <v>11775.64809999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4485.45373400001</v>
+        <v>12729.77211</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1640.39140275232</v>
+        <v>2970.954</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2929,18 +2929,18 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2580.714568752319</v>
+        <v>3119.61419</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Unmet demand: GWh</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2949,18 +2949,18 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2827.868973174669</v>
+        <v>8804.694099999992</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Imports exchange: GWh</t>
+          <t>Unmet demand: GWh</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2969,133 +2969,133 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2645.52</v>
+        <v>9610.157920000011</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Exports exchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>634.9600347523149</v>
+        <v>11775.64809999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2827.868973174669</v>
+        <v>12729.77211</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mozal</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Net interchange: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2010.559965247685</v>
+        <v>8322.000000000011</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mozal</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Demand: GWh</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.649316744344043</v>
+        <v>9.999999999999956e-09</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mozal</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Net interchange Ratio: GWh</t>
+          <t>Unmet demand: GWh</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.4482400409143716</v>
+        <v>8322.000000000011</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mozal</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Total Demand: GWh</t>
+          <t>Surplus generation: GWh</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4355.145617000001</v>
+        <v>-9.999999999999956e-09</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mozal</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3105,1430 +3105,30 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4485.45373400001</v>
+        <v>8322.000000000011</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Mozal</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Demand: GWh</t>
+          <t>Total Demand: GWh</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>14390.00000000004</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>15337.00000000001</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>23128.57678945115</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>24150.23954064875</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Exports exchange: GWh</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>8738.57678945115</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Exports exchange: GWh</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>8813.239540648743</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Net interchange: GWh</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>-8738.57678945115</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Net interchange: GWh</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>-8813.239540648743</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Net interchange Ratio: GWh</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>-0.6072673237978545</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Net interchange Ratio: GWh</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>-0.5746390780888531</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>14390.00000000004</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>15337.00000000001</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>16637.87143000001</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>17697.40276</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>15811.394292</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>17697.40276</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Unmet demand: GWh</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>826.4771380000063</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>16637.87143000001</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>17697.40276</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>12153.14516999996</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>13326.08802000002</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>12153.14516999999</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>13326.08802000001</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>12153.14516999996</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>13326.08802000002</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>7123.117210999982</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>7704.363575</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>9963.653240316589</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11172.48215965354</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Exports exchange: GWh</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>2840.536029316591</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Exports exchange: GWh</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>3450.407868805707</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Net interchange: GWh</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>-2840.536029316591</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Net interchange: GWh</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>-3450.407868805707</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Net interchange Ratio: GWh</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>-0.3987771006954723</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Net interchange Ratio: GWh</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>-0.4478511216685029</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>7123.117210999982</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>7704.363575</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>2526.620252999999</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>2722.295029999999</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>1570.871865080436</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>2372.212729313335</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Unmet demand: GWh</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>957.99835023116</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Imports exchange: GWh</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>508.014029124923</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Exports exchange: GWh</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>107.6344904958082</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Net interchange: GWh</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>400.3795386291148</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Net interchange Ratio: GWh</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>0.1470742642575059</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>2526.620252999999</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>2722.295029999999</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>11775.64809999999</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>12729.77211</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>4467.6</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Total production: GWh</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>4638.160190000001</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Unmet demand: GWh</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>1582.653393982957</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Unmet demand: GWh</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>1733.397340257066</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Imports exchange: GWh</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>5963.95281876775</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Imports exchange: GWh</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>6648.487409454454</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Net interchange: GWh</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>5963.95281876775</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Net interchange: GWh</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>6648.487409454454</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Net interchange Ratio: GWh</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>0.5064649323859938</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Net interchange Ratio: GWh</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>0.522278588493479</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>11775.64809999999</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>12729.77211</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Mozal</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>8322.000000000011</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Mozal</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>9.999999999999956e-09</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Mozal</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Surplus generation: GWh</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>15.48930903635718</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Mozal</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Surplus generation: GWh</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>-9.999999999999956e-09</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Mozal</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Imports exchange: GWh</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>8363.872753670319</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Mozal</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Net interchange: GWh</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>8363.872753670319</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Mozal</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Net interchange Ratio: GWh</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>1.005031573380234</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Mozal</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>8322.000000000011</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Mozal</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Total Demand: GWh</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
         <v>9.999999999999956e-09</v>
       </c>
     </row>
@@ -4543,7 +3143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D183"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4563,7 +3163,7 @@
         </is>
       </c>
       <c r="D1" t="n">
-        <v>0.8084816382801137</v>
+        <v>0.3827498216679686</v>
       </c>
     </row>
     <row r="2">
@@ -4583,7 +3183,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.539141052436455</v>
+        <v>0.8670816722875797</v>
       </c>
     </row>
     <row r="3">
@@ -4603,7 +3203,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.49577628869776</v>
+        <v>11.29431082856942</v>
       </c>
     </row>
     <row r="4">
@@ -4623,7 +3223,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.76433063053466</v>
+        <v>10.89272329554948</v>
       </c>
     </row>
     <row r="5">
@@ -4643,7 +3243,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.562970316619683</v>
+        <v>2.760446972963168</v>
       </c>
     </row>
     <row r="6">
@@ -4663,7 +3263,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.298212663491226</v>
+        <v>2.719212899516985</v>
       </c>
     </row>
     <row r="7">
@@ -4683,7 +3283,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>47.69698271545263</v>
+        <v>54.24501394652497</v>
       </c>
     </row>
     <row r="8">
@@ -4703,7 +3303,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>39.66363544178454</v>
+        <v>50.4821919254812</v>
       </c>
     </row>
     <row r="9">
@@ -4714,7 +3314,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4723,7 +3323,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9.800703124699446</v>
+        <v>58.46175103804185</v>
       </c>
     </row>
     <row r="10">
@@ -4734,7 +3334,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4743,18 +3343,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9.263002120684844</v>
+        <v>60.08692767789218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Export revenues with internal zones: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4763,18 +3363,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-7.674000016328834</v>
+        <v>3.138347260909935</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Export revenues with internal zones: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4783,18 +3383,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.801355812843724</v>
+        <v>2.957130358705157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4803,18 +3403,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.8048526997638212</v>
+        <v>0.2482813370473538</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4823,18 +3423,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.4797349140613985</v>
+        <v>0.2339448818897633</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Carbon costs: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4843,18 +3443,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>58.43162420188273</v>
+        <v>1227.871578458681</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>South_Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Carbon costs: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4863,7 +3463,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53.77856991840666</v>
+        <v>1301.327812773403</v>
       </c>
     </row>
     <row r="17">
@@ -4874,16 +3474,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Investment costs: $m</t>
+          <t>Unmet country planning reserve costs: $m</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.6345479698078962</v>
+        <v>9.003899721448466</v>
       </c>
     </row>
     <row r="18">
@@ -4894,27 +3494,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Unmet country planning reserve costs: $m</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.138347260909935</v>
+        <v>9.661942257217831</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Investment costs: $m</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4923,18 +3523,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.657042869641288</v>
+        <v>3.8603414997776</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4943,18 +3543,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.2813855153203342</v>
+        <v>2.427837861332567</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4963,18 +3563,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.2651375328083984</v>
+        <v>3.337624548175321</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unmet demand costs: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4983,18 +3583,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8.939854960329692</v>
+        <v>0.1152267823071475</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Unmet demand costs: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5003,18 +3603,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17.17018954078419</v>
+        <v>0.1329654858779983</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Unmet country spinning reserve costs: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5023,18 +3623,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1085007385303985</v>
+        <v>0.249577240961942</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Unmet country spinning reserve costs: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5043,18 +3643,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.07267075490359728</v>
+        <v>0.2341406412754867</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Unmet country planning reserve costs: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5063,18 +3663,18 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3.544289693593315</v>
+        <v>1737.210216220139</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Unmet country planning reserve costs: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5083,18 +3683,18 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3.467716535433064</v>
+        <v>1564.559464667791</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Unmet country spinning reserve costs: $m</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5103,18 +3703,18 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>139.5654734650403</v>
+        <v>0.0004537997703303488</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Unmet country spinning reserve costs: $m</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5123,18 +3723,18 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>192.6641130931395</v>
+        <v>0.1116829069077289</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Unmet country planning reserve costs: $m</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5143,18 +3743,18 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-37.7689201601455</v>
+        <v>9.080005095466626</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Unmet country planning reserve costs: $m</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5163,7 +3763,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-63.59761308652674</v>
+        <v>8.856360280830993</v>
       </c>
     </row>
     <row r="32">
@@ -5174,16 +3774,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Investment costs: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.959713039977669</v>
+        <v>0.05103354023347594</v>
       </c>
     </row>
     <row r="33">
@@ -5194,22 +3794,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.427837861332567</v>
+        <v>0.0500967550340302</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5219,37 +3819,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.44723231232604</v>
+        <v>14.53791015010359</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.1224208884525578</v>
+        <v>13.37964038620411</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5259,142 +3859,142 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.1151747922428073</v>
+        <v>0.5438300017306508</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Unmet country spinning reserve costs: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.5054462119910579</v>
+        <v>0.5443215801188037</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Unmet country spinning reserve costs: $m</t>
+          <t>Investment costs: $m</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.2153052532675345</v>
+        <v>0.03695448528130121</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Investment costs: $m</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>102.4955842428479</v>
+        <v>1.320585940951049</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>94.7499132916932</v>
+        <v>10.1274101651043</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-2.04991168485696</v>
+        <v>9.823783042961548</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-1.894998265833866</v>
+        <v>1.961196577558488</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Investment costs: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5403,18 +4003,18 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.37760434788883</v>
+        <v>1.893694465295343</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5423,18 +4023,18 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.53791015010359</v>
+        <v>28.02105678929401</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5443,18 +4043,18 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.80188480014853</v>
+        <v>27.81808455373544</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5463,18 +4063,18 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.394632827332989</v>
+        <v>34.6690431533</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5483,58 +4083,58 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3.124174382973132</v>
+        <v>34.46947139186434</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fuel costs: $m</t>
+          <t>Investment costs: $m</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>29.53299213999429</v>
+        <v>2.776495469889869</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fuel costs: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>27.96785556532275</v>
+        <v>7.686153499098302</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Transmission costs: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5543,18 +4143,18 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.230169170580433</v>
+        <v>7.865115019105375</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5563,18 +4163,18 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>62.32173017078649</v>
+        <v>2.267059969786632</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5583,18 +4183,18 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>56.5269729927935</v>
+        <v>1.349298983406951</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Export revenues with internal zones: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5603,18 +4203,18 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-282.6223909762871</v>
+        <v>53.9518617635371</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Export revenues with internal zones: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5623,18 +4223,18 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-243.8919273429449</v>
+        <v>32.21060364692098</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5643,18 +4243,18 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-6.558344228477637</v>
+        <v>1020.496932849473</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5663,38 +4263,38 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-5.368058367139182</v>
+        <v>1154.308237230374</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Carbon costs: $m</t>
+          <t>Unmet country spinning reserve costs: $m</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.59494790695785</v>
+        <v>0.2363151275076042</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Carbon costs: $m</t>
+          <t>Unmet country planning reserve costs: $m</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5703,18 +4303,18 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.01512572858777</v>
+        <v>1.090396491122239</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Investment costs: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5723,18 +4323,18 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.03695448528130121</v>
+        <v>31.44871326418327</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Investment costs: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5743,33 +4343,33 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.118306354355334</v>
+        <v>24.29655716776744</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Investment costs: $m</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.1274101651043</v>
+        <v>4.234409402839336</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5779,37 +4379,37 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>9.730971564465445</v>
+        <v>5.029508063863204</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.755526408226635</v>
+        <v>6.826653849507732</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5819,37 +4419,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1.717546837865615</v>
+        <v>0.1965541249056792</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fuel costs: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>22.149384718181</v>
+        <v>0.3900479058171101</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5859,137 +4459,137 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>22.23601591223679</v>
+        <v>0.6700960004059103</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>46.47089191304095</v>
+        <v>3.104765348990152</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>41.75147315930212</v>
+        <v>1514.958877132765</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Export revenues with internal zones: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-62.91420663453822</v>
+        <v>1019.479669697113</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Export revenues with internal zones: $m</t>
+          <t>Unmet country planning reserve costs: $m</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-56.23225228718777</v>
+        <v>3.878037342327513</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Unmet country planning reserve costs: $m</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-24.25288921888152</v>
+        <v>3.529983807341612</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-21.26002008245933</v>
+        <v>0.6128815184979247</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5999,42 +4599,42 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>27.38462632190436</v>
+        <v>0.6209045080031402</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Carbon costs: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28.06468698922894</v>
+        <v>11.19886726893673</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Investment costs: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6043,18 +4643,18 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5.405336506744078</v>
+        <v>10.50738084371128</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6063,18 +4663,18 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7.686153499098302</v>
+        <v>0.9063665908500955</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6083,18 +4683,18 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>8.781584567182595</v>
+        <v>0.8843623422007497</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6103,18 +4703,18 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.7868093370383965</v>
+        <v>6.533707059580645</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6123,18 +4723,18 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.7242314939839125</v>
+        <v>5.644535856303325</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fuel costs: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6143,18 +4743,18 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.27914298138824</v>
+        <v>8.105739744964295</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fuel costs: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6163,18 +4763,18 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.1020305500077</v>
+        <v>7.93533051799116</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Unmet country spinning reserve costs: $m</t>
+          <t>Investment costs: $m</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6183,18 +4783,18 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.6570599386996158</v>
+        <v>24.35256902883199</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6203,18 +4803,18 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>137.7931759987964</v>
+        <v>11.1041041684501</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6223,18 +4823,18 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>121.2434310922767</v>
+        <v>15.37647423129562</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Export revenues with internal zones: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6243,18 +4843,18 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-31.41211919711375</v>
+        <v>0.5378140300667056</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Export revenues with internal zones: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6263,18 +4863,18 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-44.73219297927518</v>
+        <v>0.5368854319248141</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Investment costs: $m</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6283,18 +4883,18 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-10.27852194534621</v>
+        <v>0.7042430698326374</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Investment costs: $m</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6303,18 +4903,18 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-8.449813908102342</v>
+        <v>4.328019980994586</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Carbon costs: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6323,18 +4923,18 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>17.7147545387037</v>
+        <v>12.05970125015799</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Carbon costs: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6343,118 +4943,118 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>17.01355342545934</v>
+        <v>12.35286002560861</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Investment costs: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>4.234409402839336</v>
+        <v>1.566742639941608</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5.029508063863204</v>
+        <v>1.382372878226978</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6.826653849507732</v>
+        <v>18.02825639565224</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.1670782251283277</v>
+        <v>16.09702748103952</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.3614283182936901</v>
+        <v>8.604947810417482</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Fuel costs: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6463,18 +5063,18 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2.490049092545155</v>
+        <v>7.784917871681778</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6483,18 +5083,18 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>98.74549047663764</v>
+        <v>7.741616256832382</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Import costs with internal zones: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6503,293 +5103,293 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>79.14672517911968</v>
+        <v>7.15755940944155</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Export revenues with internal zones: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>-18.97800632855467</v>
+        <v>0.5500000000000013</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>-31.50504388329253</v>
+        <v>0.5500000000000003</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Unmet country planning reserve costs: $m</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-26.21049715132983</v>
+        <v>4.283268650777105</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>DRC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Unmet country planning reserve costs: $m</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.19886726893673</v>
+        <v>4.718381723322691</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Investment costs: $m</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.50738084371128</v>
+        <v>0.4953289512144228</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Investment costs: $m</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.8780779135879784</v>
+        <v>2.234135231807734</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.8604978607087248</v>
+        <v>8.704434302656564</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Fuel costs: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.006521437187168285</v>
+        <v>8.596441510602915</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Fuel costs: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.00563393578896754</v>
+        <v>0.9197404554082111</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Export revenues with internal zones: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>-0.3339970280888196</v>
+        <v>0.8687989127645325</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Export revenues with internal zones: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>-0.316051492948869</v>
+        <v>25.83986721894206</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Fuel costs: $m</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>-156.0820107566179</v>
+        <v>24.45177667524188</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Trade shared benefits: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>-148.8563384331364</v>
+        <v>69.37556565621685</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Carbon costs: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.008090517698494878</v>
+        <v>84.2610490195602</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6799,22 +5399,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.007920428488849393</v>
+        <v>5.357598933072815</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Investment costs: $m</t>
+          <t>Carbon costs: $m</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6823,33 +5423,33 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>24.2613141156648</v>
+        <v>5.303221686144965</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fixed O&amp;M: $m</t>
+          <t>Investment costs: $m</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1041041684501</v>
+        <v>0.8343849102471181</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6859,37 +5459,37 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>15.34850402534434</v>
+        <v>2.215801608405742</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Variable O&amp;M: $m</t>
+          <t>Fixed O&amp;M: $m</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1.534280121754734</v>
+        <v>2.426791283697223</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6899,57 +5499,57 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.5561392418535472</v>
+        <v>0.1387630375945084</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Fuel costs: $m</t>
+          <t>Variable O&amp;M: $m</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>37.77147119902025</v>
+        <v>0.1283624471734553</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Fuel costs: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.7754219233987885</v>
+        <v>1869.258920024962</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6959,22 +5559,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>124.1861288382377</v>
+        <v>1887.338955669648</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Carbon costs: $m</t>
+          <t>Unmet country planning reserve costs: $m</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6983,18 +5583,18 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>12.01599666797918</v>
+        <v>4.283268650777105</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>DRC_South</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Carbon costs: $m</t>
+          <t>Unmet country planning reserve costs: $m</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7003,18 +5603,18 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.3885759393942279</v>
+        <v>4.718381723322692</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Mozal</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Investment costs: $m</t>
+          <t>Unmet demand costs: $m</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7023,1187 +5623,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.7042430698326374</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Investment costs: $m</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>4.44012298011808</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Fixed O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>12.05970125015799</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Fixed O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>12.41289264724516</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Variable O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>3.416002398455682</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Variable O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>3.018575632483327</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Fuel costs: $m</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>51.51656961140246</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Fuel costs: $m</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>46.22414454351919</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Carbon costs: $m</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>24.8980414023915</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Carbon costs: $m</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>22.7885748472994</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Investment costs: $m</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>3.468487333239717</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Investment costs: $m</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>8.68596081661136</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Fixed O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>8.353707827257056</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Fixed O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>8.952062506822529</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Variable O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>0.7744107200964795</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Variable O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>0.7977864181718792</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Fuel costs: $m</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>0.2229837162616259</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Fuel costs: $m</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>0.05869563332865207</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Unmet country spinning reserve costs: $m</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>0.2874765944817037</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Unmet country spinning reserve costs: $m</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>9.222802613488653e-05</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Unmet country planning reserve costs: $m</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>2.780789545252007</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Unmet country planning reserve costs: $m</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>2.457789097330739</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Export revenues with internal zones: $m</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>-665.6520256030435</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Export revenues with internal zones: $m</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>-15.26795838983413</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Trade shared benefits: $m</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>-13.86775053339672</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Trade shared benefits: $m</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>-372.1012174059802</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Carbon costs: $m</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>0.04559569779434715</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>DRC</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Carbon costs: $m</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>0.01255852357973615</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Investment costs: $m</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>0.4953289512144228</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Investment costs: $m</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>7.104912178366792</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Fixed O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>8.704434302656564</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Fixed O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>9.992322544114554</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Variable O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>0.8906409668520928</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Variable O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>1.311080167897893</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Fuel costs: $m</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>35.65464112398741</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Fuel costs: $m</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>20.22665723502357</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Transmission costs: $m</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>3.711769644859475</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Unmet demand costs: $m</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>947.9049622649802</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Import costs with internal zones: $m</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>24.78491291740183</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Export revenues with internal zones: $m</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>-4.986434323399484</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Trade shared benefits: $m</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>-0.06487077790869332</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Carbon costs: $m</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>7.36452335068019</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Carbon costs: $m</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.1358913112162</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Investment costs: $m</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>1.005312164063548</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Fixed O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>2.215801608405742</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Fixed O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>2.615325687868893</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Variable O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>0.2086662219466292</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Variable O&amp;M: $m</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>0.1930262363510606</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Unmet demand costs: $m</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>336.0013352434839</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Unmet demand costs: $m</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>340.4219111855465</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Unmet country spinning reserve costs: $m</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>0.2874765944817037</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Unmet country spinning reserve costs: $m</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>9.222802613488653e-05</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Unmet country planning reserve costs: $m</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>2.780789545252006</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Unmet country planning reserve costs: $m</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>2.457789097330739</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Import costs with internal zones: $m</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>738.7125052682735</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Import costs with internal zones: $m</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>764.2086934098888</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Trade shared benefits: $m</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>-167.9560732527471</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>DRC_South</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Trade shared benefits: $m</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>-377.4149914989381</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Mozal</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Import costs with internal zones: $m</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>85.29668296874338</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Mozal</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Trade shared benefits: $m</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>30.65633176608592</v>
+        <v>2499.999999999996</v>
       </c>
     </row>
   </sheetData>
